--- a/www/ig/fhir/tddui/ValueSet-tddui-encounter-participant.xlsx
+++ b/www/ig/fhir/tddui/ValueSet-tddui-encounter-participant.xlsx
@@ -7,14 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Include ValueSet #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include ValueSet #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T14:53:05+00:00</t>
+    <t>2026-03-16T15:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -98,21 +97,6 @@
   </si>
   <si>
     <t>BooleanType[null]</t>
-  </si>
-  <si>
-    <t>Codes</t>
-  </si>
-  <si>
-    <t>All codes</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-encounter-participant</t>
   </si>
   <si>
     <t>ValueSet URL</t>
@@ -382,7 +366,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -399,46 +383,6 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>34</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/www/ig/fhir/tddui/ValueSet-tddui-encounter-participant.xlsx
+++ b/www/ig/fhir/tddui/ValueSet-tddui-encounter-participant.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:53:20+00:00</t>
+    <t>2026-07-22T14:44:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
